--- a/Team-Data/2007-08/3-14-2007-08.xlsx
+++ b/Team-Data/2007-08/3-14-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
         <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>0.415</v>
+        <v>0.406</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J2" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.347</v>
+        <v>0.342</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P2" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R2" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T2" t="n">
         <v>42.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="V2" t="n">
         <v>15.3</v>
@@ -730,31 +797,31 @@
         <v>20.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.2</v>
+        <v>95.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
         <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -763,19 +830,19 @@
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -790,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>26</v>
@@ -811,10 +878,10 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.797</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,67 +928,67 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K3" t="n">
         <v>0.476</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
         <v>19.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.386</v>
+        <v>0.388</v>
       </c>
       <c r="O3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P3" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U3" t="n">
         <v>22.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
         <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z3" t="n">
         <v>22.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -957,10 +1024,10 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
@@ -969,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -984,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>0.369</v>
+        <v>0.375</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,10 +1110,10 @@
         <v>35.7</v>
       </c>
       <c r="J4" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>6.4</v>
@@ -1055,13 +1122,13 @@
         <v>17.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O4" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>0.709</v>
@@ -1076,10 +1143,10 @@
         <v>40.7</v>
       </c>
       <c r="U4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.5</v>
@@ -1094,16 +1161,16 @@
         <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
         <v>-4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
@@ -1133,13 +1200,13 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
@@ -1148,22 +1215,22 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1175,7 +1242,7 @@
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.429</v>
@@ -1234,7 +1301,7 @@
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
         <v>0.353</v>
@@ -1243,10 +1310,10 @@
         <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R5" t="n">
         <v>13.5</v>
@@ -1258,46 +1325,46 @@
         <v>43.7</v>
       </c>
       <c r="U5" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA5" t="n">
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC5" t="n">
         <v>-2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1321,7 +1388,7 @@
         <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1342,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1360,7 +1427,7 @@
         <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1491,7 +1558,7 @@
         <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
         <v>10</v>
@@ -1500,7 +1567,7 @@
         <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.652</v>
+        <v>0.646</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M7" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S7" t="n">
         <v>32.2</v>
       </c>
       <c r="T7" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W7" t="n">
         <v>6</v>
@@ -1634,25 +1701,25 @@
         <v>4.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA7" t="n">
         <v>21.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1664,7 +1731,7 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1673,7 +1740,7 @@
         <v>7</v>
       </c>
       <c r="AL7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
         <v>20</v>
@@ -1682,10 +1749,10 @@
         <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1718,13 +1785,13 @@
         <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -1753,61 +1820,61 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="J8" t="n">
         <v>85.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L8" t="n">
         <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.346</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.754</v>
+        <v>0.751</v>
       </c>
       <c r="R8" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S8" t="n">
         <v>32.8</v>
       </c>
       <c r="T8" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U8" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W8" t="n">
         <v>9.1</v>
@@ -1819,19 +1886,19 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
         <v>23.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>108</v>
+        <v>107.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1852,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL8" t="n">
         <v>14</v>
@@ -1873,10 +1940,10 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>3</v>
@@ -1885,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
@@ -1897,7 +1964,7 @@
         <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.723</v>
+        <v>0.719</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,37 +2020,37 @@
         <v>36.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.367</v>
+        <v>0.372</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P9" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S9" t="n">
         <v>29.4</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
         <v>22.6</v>
@@ -1992,7 +2059,7 @@
         <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X9" t="n">
         <v>5.5</v>
@@ -2001,19 +2068,19 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,19 +2098,19 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2055,16 +2122,16 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
         <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2079,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>23</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2228,10 +2295,10 @@
         <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L11" t="n">
         <v>7.2</v>
       </c>
       <c r="M11" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="O11" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
         <v>22.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.72</v>
+        <v>0.723</v>
       </c>
       <c r="R11" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
         <v>32.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V11" t="n">
         <v>14.2</v>
@@ -2365,28 +2432,28 @@
         <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA11" t="n">
         <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
@@ -2401,28 +2468,28 @@
         <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
       </c>
       <c r="AP11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>26</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>28</v>
-      </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>2</v>
@@ -2431,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
         <v>15</v>
@@ -2443,13 +2510,13 @@
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -2481,61 +2548,61 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>0.385</v>
+        <v>0.391</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J12" t="n">
         <v>85.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="P12" t="n">
         <v>24.3</v>
       </c>
-      <c r="N12" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="O12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>24.4</v>
-      </c>
       <c r="Q12" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V12" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.5</v>
@@ -2547,19 +2614,19 @@
         <v>5.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB12" t="n">
         <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2589,19 +2656,19 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,10 +2748,10 @@
         <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>4.3</v>
@@ -2702,19 +2769,19 @@
         <v>26.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="R13" t="n">
         <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
@@ -2729,7 +2796,7 @@
         <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA13" t="n">
         <v>21.8</v>
@@ -2738,16 +2805,16 @@
         <v>93.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2765,7 +2832,7 @@
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
         <v>26</v>
@@ -2774,7 +2841,7 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -2783,7 +2850,7 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
         <v>15</v>
@@ -2798,7 +2865,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>16</v>
@@ -2813,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
         <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J14" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
         <v>21.5</v>
@@ -2890,7 +2957,7 @@
         <v>10.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T14" t="n">
         <v>44.1</v>
@@ -2899,7 +2966,7 @@
         <v>24</v>
       </c>
       <c r="V14" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.199999999999999</v>
@@ -2908,22 +2975,22 @@
         <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
         <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.2</v>
+        <v>108.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2950,10 +3017,10 @@
         <v>6</v>
       </c>
       <c r="AM14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-7</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3117,10 +3184,10 @@
         <v>28</v>
       </c>
       <c r="AH15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI15" t="n">
         <v>14</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>14</v>
@@ -3138,10 +3205,10 @@
         <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3168,10 +3235,10 @@
         <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>0.172</v>
+        <v>0.175</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,40 +3294,40 @@
         <v>35.5</v>
       </c>
       <c r="J16" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P16" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R16" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="U16" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
         <v>14.9</v>
@@ -3269,16 +3336,16 @@
         <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
         <v>93.7</v>
@@ -3287,7 +3354,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3320,19 +3387,19 @@
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3341,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW16" t="n">
         <v>18</v>
@@ -3356,10 +3423,10 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3499,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>24</v>
@@ -3520,7 +3587,7 @@
         <v>23</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
@@ -3541,7 +3608,7 @@
         <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -3573,49 +3640,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
         <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>0.234</v>
+        <v>0.222</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J18" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
       <c r="R18" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S18" t="n">
         <v>29.4</v>
@@ -3627,10 +3694,10 @@
         <v>19.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W18" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
@@ -3639,28 +3706,28 @@
         <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.2</v>
+        <v>-7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF18" t="n">
         <v>27</v>
       </c>
       <c r="AG18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH18" t="n">
         <v>28</v>
@@ -3672,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,34 +3748,34 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
       </c>
       <c r="AT18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3723,7 +3790,7 @@
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3887,7 +3954,7 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>23</v>
@@ -3896,7 +3963,7 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J20" t="n">
         <v>83.3</v>
@@ -3961,37 +4028,37 @@
         <v>0.463</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
         <v>20</v>
       </c>
       <c r="N20" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="O20" t="n">
         <v>15.4</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T20" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
@@ -4000,31 +4067,31 @@
         <v>3.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA20" t="n">
         <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH20" t="n">
         <v>7</v>
@@ -4078,7 +4145,7 @@
         <v>28</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>1</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,10 +4276,10 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
         <v>18</v>
@@ -4233,7 +4300,7 @@
         <v>13</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>22</v>
@@ -4251,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.642</v>
+        <v>0.636</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,7 +4386,7 @@
         <v>37.2</v>
       </c>
       <c r="J22" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K22" t="n">
         <v>0.474</v>
@@ -4328,25 +4395,25 @@
         <v>9.4</v>
       </c>
       <c r="M22" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P22" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.727</v>
       </c>
       <c r="R22" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T22" t="n">
         <v>42.2</v>
@@ -4358,16 +4425,16 @@
         <v>14.4</v>
       </c>
       <c r="W22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X22" t="n">
         <v>4.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA22" t="n">
         <v>23.7</v>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
         <v>10</v>
@@ -4397,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4412,25 +4479,25 @@
         <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>13</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4439,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
         <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.485</v>
+        <v>0.477</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
         <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>3.5</v>
       </c>
       <c r="M23" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.318</v>
+        <v>0.316</v>
       </c>
       <c r="O23" t="n">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="P23" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.707</v>
+        <v>0.702</v>
       </c>
       <c r="R23" t="n">
         <v>13.1</v>
       </c>
       <c r="S23" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
         <v>8.5</v>
@@ -4552,19 +4619,19 @@
         <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
         <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,10 +4661,10 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,13 +4673,13 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT23" t="n">
         <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>17</v>
@@ -4621,19 +4688,19 @@
         <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AY23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>4.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>7</v>
@@ -4755,7 +4822,7 @@
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>2</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4809,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4940,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
@@ -4955,7 +5022,7 @@
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>22</v>
@@ -4964,7 +5031,7 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -4997,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,13 +5186,13 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
         <v>12</v>
@@ -5167,7 +5234,7 @@
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
         <v>44</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>0.677</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
@@ -5241,13 +5308,13 @@
         <v>20.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O27" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.757</v>
@@ -5256,13 +5323,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T27" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U27" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V27" t="n">
         <v>12.9</v>
@@ -5280,58 +5347,58 @@
         <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.5</v>
+        <v>95.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
         <v>15</v>
       </c>
       <c r="AL27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM27" t="n">
         <v>7</v>
       </c>
-      <c r="AM27" t="n">
-        <v>8</v>
-      </c>
       <c r="AN27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
         <v>10</v>
@@ -5340,7 +5407,7 @@
         <v>19</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5361,10 +5428,10 @@
         <v>25</v>
       </c>
       <c r="BB27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
-        <v>0.242</v>
+        <v>0.246</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J28" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K28" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L28" t="n">
         <v>4</v>
@@ -5423,13 +5490,13 @@
         <v>11.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0.768</v>
@@ -5438,52 +5505,52 @@
         <v>11.8</v>
       </c>
       <c r="S28" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="T28" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V28" t="n">
         <v>16.5</v>
       </c>
       <c r="W28" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X28" t="n">
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="AC28" t="n">
-        <v>-8</v>
+        <v>-8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG28" t="n">
         <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5504,7 +5571,7 @@
         <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5534,7 +5601,7 @@
         <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ28" t="n">
         <v>13</v>
@@ -5543,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
         <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.523</v>
+        <v>0.531</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L29" t="n">
         <v>7.4</v>
       </c>
       <c r="M29" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.404</v>
+        <v>0.406</v>
       </c>
       <c r="O29" t="n">
         <v>16.8</v>
       </c>
       <c r="P29" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.800000000000001</v>
@@ -5623,13 +5690,13 @@
         <v>30.4</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U29" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -5644,16 +5711,16 @@
         <v>19.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5686,16 +5753,16 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>27</v>
@@ -5719,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5728,7 +5795,7 @@
         <v>10</v>
       </c>
       <c r="BC29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.657</v>
+        <v>0.652</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,7 +5842,7 @@
         <v>39.9</v>
       </c>
       <c r="J30" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K30" t="n">
         <v>0.496</v>
@@ -5787,16 +5854,16 @@
         <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O30" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R30" t="n">
         <v>11.3</v>
@@ -5808,37 +5875,37 @@
         <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AA30" t="n">
         <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5865,22 +5932,22 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5898,7 +5965,7 @@
         <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6047,7 +6114,7 @@
         <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6080,7 +6147,7 @@
         <v>9</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-14-2007-08</t>
+          <t>2008-03-14</t>
         </is>
       </c>
     </row>
